--- a/Plannings 2026 S25.xlsx
+++ b/Plannings 2026 S25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BE0CE18-006B-4DAE-B16C-37980937CBF9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="141">
   <si>
     <t>Planning des salariés du 15/06/2026 au 21/06/2026</t>
   </si>
@@ -153,6 +153,9 @@
     <t>15:15/17:45</t>
   </si>
   <si>
+    <t>14:00/17:00</t>
+  </si>
+  <si>
     <t>REU</t>
   </si>
   <si>
@@ -312,9 +315,6 @@
     <t>08:45/16:00</t>
   </si>
   <si>
-    <t>08:45/17:30</t>
-  </si>
-  <si>
     <t>10:00/17:00</t>
   </si>
   <si>
@@ -414,9 +414,6 @@
     <t>13:45/19:45</t>
   </si>
   <si>
-    <t>14:00/16:30</t>
-  </si>
-  <si>
     <t>11:45/16:00</t>
   </si>
   <si>
@@ -442,6 +439,12 @@
   </si>
   <si>
     <t>EDF // ANNIV</t>
+  </si>
+  <si>
+    <t>17:00/22:20</t>
+  </si>
+  <si>
+    <t>08:45/17:00</t>
   </si>
 </sst>
 </file>
@@ -5746,25 +5749,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="D3" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="G3" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>139</v>
-      </c>
       <c r="H3" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5973,10 +5976,10 @@
         <v>29</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17" s="64" t="s">
         <v>30</v>
@@ -5991,10 +5994,10 @@
       <c r="A18" s="25"/>
       <c r="B18" s="64"/>
       <c r="C18" s="65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D18" s="65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="64"/>
@@ -6005,10 +6008,10 @@
       <c r="A19" s="25"/>
       <c r="B19" s="64"/>
       <c r="C19" s="66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D19" s="66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E19" s="64"/>
       <c r="F19" s="64"/>
@@ -6033,10 +6036,10 @@
       <c r="A21" s="21"/>
       <c r="B21" s="70"/>
       <c r="C21" s="70" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D21" s="70" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
@@ -6082,7 +6085,7 @@
         <v>34</v>
       </c>
       <c r="H23" s="54" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -6109,8 +6112,8 @@
       <c r="G25" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="24" t="s">
-        <v>35</v>
+      <c r="H25" s="71" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6157,7 +6160,7 @@
         <v>38</v>
       </c>
       <c r="C28" s="58" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D28" s="43" t="s">
         <v>38</v>
@@ -6172,16 +6175,16 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
       <c r="B29" s="41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -6194,7 +6197,7 @@
         <v>38</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -6205,10 +6208,10 @@
       <c r="A31" s="25"/>
       <c r="B31" s="41"/>
       <c r="C31" s="41" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -6219,7 +6222,7 @@
       <c r="A32" s="25"/>
       <c r="B32" s="41"/>
       <c r="C32" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D32" s="43" t="s">
         <v>38</v>
@@ -6233,10 +6236,10 @@
       <c r="A33" s="25"/>
       <c r="B33" s="41"/>
       <c r="C33" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -6259,7 +6262,7 @@
       <c r="A35" s="31"/>
       <c r="B35" s="41"/>
       <c r="C35" s="41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D35" s="41"/>
       <c r="E35" s="1"/>
@@ -6269,7 +6272,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
@@ -6288,7 +6291,7 @@
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
       <c r="D37" s="42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="23"/>
@@ -6299,7 +6302,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B38" s="40" t="s">
         <v>12</v>
@@ -6308,7 +6311,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>15</v>
@@ -6324,19 +6327,19 @@
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="25"/>
       <c r="B39" s="41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="41" t="s">
         <v>58</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>57</v>
       </c>
       <c r="G39" s="41" t="s">
         <v>13</v>
@@ -6362,12 +6365,12 @@
       <c r="B41" s="41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="41"/>
       <c r="G41" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H41" s="26"/>
     </row>
@@ -6376,7 +6379,7 @@
       <c r="B42" s="41"/>
       <c r="C42" s="1"/>
       <c r="D42" s="43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="41"/>
@@ -6388,7 +6391,7 @@
       <c r="B43" s="41"/>
       <c r="C43" s="1"/>
       <c r="D43" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="41"/>
@@ -6400,7 +6403,7 @@
       <c r="B44" s="41"/>
       <c r="C44" s="1"/>
       <c r="D44" s="59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="41"/>
@@ -6412,7 +6415,7 @@
       <c r="B45" s="42"/>
       <c r="C45" s="23"/>
       <c r="D45" s="60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45" s="23"/>
       <c r="F45" s="42"/>
@@ -6421,7 +6424,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -6440,7 +6443,7 @@
       <c r="B47" s="23"/>
       <c r="C47" s="23"/>
       <c r="D47" s="23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E47" s="23" t="s">
         <v>16</v>
@@ -6470,12 +6473,12 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H49" s="26"/>
     </row>
@@ -6498,12 +6501,12 @@
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="49" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H51" s="26"/>
     </row>
@@ -6524,7 +6527,7 @@
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -6548,7 +6551,7 @@
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="23"/>
@@ -6557,7 +6560,7 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B56" s="33"/>
       <c r="C56" s="34"/>
@@ -6569,7 +6572,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
@@ -6590,12 +6593,12 @@
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
       <c r="H58" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B59" s="28"/>
       <c r="C59" s="29"/>
@@ -6607,7 +6610,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -6626,23 +6629,23 @@
       <c r="D61" s="23"/>
       <c r="E61" s="23"/>
       <c r="F61" s="42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G61" s="23"/>
       <c r="H61" s="24"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B62" s="61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C62" s="61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D62" s="61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
@@ -6652,13 +6655,13 @@
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="21"/>
       <c r="B63" s="60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C63" s="60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D63" s="60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E63" s="23"/>
       <c r="F63" s="23"/>
@@ -6667,7 +6670,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
@@ -6675,7 +6678,7 @@
       <c r="E64" s="19"/>
       <c r="F64" s="19"/>
       <c r="G64" s="48" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H64" s="20" t="s">
         <v>15</v>
@@ -6692,7 +6695,7 @@
         <v>129</v>
       </c>
       <c r="H65" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -6704,7 +6707,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="49"/>
       <c r="H66" s="53" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -6716,7 +6719,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="49"/>
       <c r="H67" s="51" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -6740,7 +6743,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="49"/>
       <c r="H69" s="26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -6752,7 +6755,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="49"/>
       <c r="H70" s="53" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6764,12 +6767,12 @@
       <c r="F71" s="23"/>
       <c r="G71" s="47"/>
       <c r="H71" s="52" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B72" s="19"/>
       <c r="C72" s="61" t="s">
@@ -6785,7 +6788,7 @@
       <c r="A73" s="25"/>
       <c r="B73" s="1"/>
       <c r="C73" s="62" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -6797,7 +6800,7 @@
       <c r="A74" s="25"/>
       <c r="B74" s="1"/>
       <c r="C74" s="59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -6809,7 +6812,7 @@
       <c r="A75" s="25"/>
       <c r="B75" s="1"/>
       <c r="C75" s="62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -6833,7 +6836,7 @@
       <c r="A77" s="21"/>
       <c r="B77" s="23"/>
       <c r="C77" s="60" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D77" s="23"/>
       <c r="E77" s="23"/>
@@ -6843,7 +6846,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="40" t="s">
@@ -6861,19 +6864,19 @@
       <c r="A79" s="31"/>
       <c r="B79" s="1"/>
       <c r="C79" s="41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="26"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B80" s="37"/>
       <c r="C80" s="37"/>
@@ -6882,7 +6885,7 @@
       </c>
       <c r="E80" s="19"/>
       <c r="F80" s="56" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>15</v>
@@ -6896,17 +6899,17 @@
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
       <c r="D81" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H81" s="26" t="s">
         <v>96</v>
+      </c>
+      <c r="H81" s="69" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -6946,7 +6949,7 @@
         <v>15</v>
       </c>
       <c r="H84" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -6960,7 +6963,7 @@
         <v>99</v>
       </c>
       <c r="H85" s="51" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -6971,7 +6974,7 @@
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H86" s="51"/>
     </row>
@@ -6983,7 +6986,7 @@
       <c r="E87" s="23"/>
       <c r="F87" s="23"/>
       <c r="G87" s="47" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H87" s="52"/>
     </row>
@@ -7006,7 +7009,7 @@
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
@@ -7051,10 +7054,10 @@
         <v>15</v>
       </c>
       <c r="G92" s="48" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H92" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -7069,10 +7072,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="49" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H93" s="51" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -7111,7 +7114,7 @@
       <c r="E96" s="19"/>
       <c r="F96" s="19"/>
       <c r="G96" s="40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H96" s="20"/>
     </row>
@@ -7120,7 +7123,7 @@
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -7149,7 +7152,7 @@
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H99" s="26"/>
     </row>
@@ -7161,7 +7164,7 @@
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H100" s="26"/>
     </row>
@@ -7406,7 +7409,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7423,7 +7426,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7440,7 +7443,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7457,7 +7460,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -7474,7 +7477,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -7491,7 +7494,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -7508,7 +7511,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7525,7 +7528,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7542,7 +7545,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7559,7 +7562,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7576,7 +7579,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7593,7 +7596,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7610,7 +7613,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7779,7 +7782,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7970,13 +7973,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F85ADEAF-2002-4827-B3D6-D214DB58F7D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2DAF3E2-8384-4621-B8C6-B2A168FC61AC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5314DF2-91A6-4B2E-8BCF-79E8C322F210}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1C5A47-85D1-4798-8C90-807825EC8D38}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EC6BF42-E38B-4470-B256-2F00664E7FEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{670A9ECD-95E7-439F-8A86-DBB1C41334FE}"/>
 </file>
--- a/Plannings 2026 S25.xlsx
+++ b/Plannings 2026 S25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BE0CE18-006B-4DAE-B16C-37980937CBF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="140">
   <si>
     <t>Planning des salariés du 15/06/2026 au 21/06/2026</t>
   </si>
@@ -153,9 +153,6 @@
     <t>15:15/17:45</t>
   </si>
   <si>
-    <t>14:00/17:00</t>
-  </si>
-  <si>
     <t>REU</t>
   </si>
   <si>
@@ -315,6 +312,9 @@
     <t>08:45/16:00</t>
   </si>
   <si>
+    <t>08:45/17:30</t>
+  </si>
+  <si>
     <t>10:00/17:00</t>
   </si>
   <si>
@@ -414,6 +414,9 @@
     <t>13:45/19:45</t>
   </si>
   <si>
+    <t>14:00/16:30</t>
+  </si>
+  <si>
     <t>11:45/16:00</t>
   </si>
   <si>
@@ -439,12 +442,6 @@
   </si>
   <si>
     <t>EDF // ANNIV</t>
-  </si>
-  <si>
-    <t>17:00/22:20</t>
-  </si>
-  <si>
-    <t>08:45/17:00</t>
   </si>
 </sst>
 </file>
@@ -5749,25 +5746,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5976,10 +5973,10 @@
         <v>29</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E17" s="64" t="s">
         <v>30</v>
@@ -5994,10 +5991,10 @@
       <c r="A18" s="25"/>
       <c r="B18" s="64"/>
       <c r="C18" s="65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D18" s="65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E18" s="64"/>
       <c r="F18" s="64"/>
@@ -6008,10 +6005,10 @@
       <c r="A19" s="25"/>
       <c r="B19" s="64"/>
       <c r="C19" s="66" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D19" s="66" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E19" s="64"/>
       <c r="F19" s="64"/>
@@ -6036,10 +6033,10 @@
       <c r="A21" s="21"/>
       <c r="B21" s="70"/>
       <c r="C21" s="70" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D21" s="70" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E21" s="70"/>
       <c r="F21" s="70"/>
@@ -6085,7 +6082,7 @@
         <v>34</v>
       </c>
       <c r="H23" s="54" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -6112,8 +6109,8 @@
       <c r="G25" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="71" t="s">
-        <v>139</v>
+      <c r="H25" s="24" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6160,7 +6157,7 @@
         <v>38</v>
       </c>
       <c r="C28" s="58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D28" s="43" t="s">
         <v>38</v>
@@ -6175,16 +6172,16 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
       <c r="B29" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="D29" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="41" t="s">
+      <c r="E29" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -6197,7 +6194,7 @@
         <v>38</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -6208,10 +6205,10 @@
       <c r="A31" s="25"/>
       <c r="B31" s="41"/>
       <c r="C31" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -6222,7 +6219,7 @@
       <c r="A32" s="25"/>
       <c r="B32" s="41"/>
       <c r="C32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D32" s="43" t="s">
         <v>38</v>
@@ -6236,10 +6233,10 @@
       <c r="A33" s="25"/>
       <c r="B33" s="41"/>
       <c r="C33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="41" t="s">
         <v>52</v>
-      </c>
-      <c r="D33" s="41" t="s">
-        <v>53</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -6262,7 +6259,7 @@
       <c r="A35" s="31"/>
       <c r="B35" s="41"/>
       <c r="C35" s="41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D35" s="41"/>
       <c r="E35" s="1"/>
@@ -6272,7 +6269,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
@@ -6291,7 +6288,7 @@
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
       <c r="D37" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="23"/>
@@ -6302,7 +6299,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" s="40" t="s">
         <v>12</v>
@@ -6311,7 +6308,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>15</v>
@@ -6327,19 +6324,19 @@
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="25"/>
       <c r="B39" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="F39" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G39" s="41" t="s">
         <v>13</v>
@@ -6365,12 +6362,12 @@
       <c r="B41" s="41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="41"/>
       <c r="G41" s="41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H41" s="26"/>
     </row>
@@ -6379,7 +6376,7 @@
       <c r="B42" s="41"/>
       <c r="C42" s="1"/>
       <c r="D42" s="43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="41"/>
@@ -6391,7 +6388,7 @@
       <c r="B43" s="41"/>
       <c r="C43" s="1"/>
       <c r="D43" s="41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="41"/>
@@ -6403,7 +6400,7 @@
       <c r="B44" s="41"/>
       <c r="C44" s="1"/>
       <c r="D44" s="59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="41"/>
@@ -6415,7 +6412,7 @@
       <c r="B45" s="42"/>
       <c r="C45" s="23"/>
       <c r="D45" s="60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45" s="23"/>
       <c r="F45" s="42"/>
@@ -6424,7 +6421,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -6443,7 +6440,7 @@
       <c r="B47" s="23"/>
       <c r="C47" s="23"/>
       <c r="D47" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E47" s="23" t="s">
         <v>16</v>
@@ -6473,12 +6470,12 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H49" s="26"/>
     </row>
@@ -6501,12 +6498,12 @@
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H51" s="26"/>
     </row>
@@ -6527,7 +6524,7 @@
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -6551,7 +6548,7 @@
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="23"/>
@@ -6560,7 +6557,7 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B56" s="33"/>
       <c r="C56" s="34"/>
@@ -6572,7 +6569,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
@@ -6593,12 +6590,12 @@
       <c r="F58" s="23"/>
       <c r="G58" s="23"/>
       <c r="H58" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B59" s="28"/>
       <c r="C59" s="29"/>
@@ -6610,7 +6607,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -6629,23 +6626,23 @@
       <c r="D61" s="23"/>
       <c r="E61" s="23"/>
       <c r="F61" s="42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G61" s="23"/>
       <c r="H61" s="24"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B62" s="61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C62" s="61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D62" s="61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
@@ -6655,13 +6652,13 @@
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="21"/>
       <c r="B63" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="D63" s="60" t="s">
         <v>79</v>
-      </c>
-      <c r="C63" s="60" t="s">
-        <v>79</v>
-      </c>
-      <c r="D63" s="60" t="s">
-        <v>80</v>
       </c>
       <c r="E63" s="23"/>
       <c r="F63" s="23"/>
@@ -6670,7 +6667,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
@@ -6678,7 +6675,7 @@
       <c r="E64" s="19"/>
       <c r="F64" s="19"/>
       <c r="G64" s="48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H64" s="20" t="s">
         <v>15</v>
@@ -6695,7 +6692,7 @@
         <v>129</v>
       </c>
       <c r="H65" s="26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -6707,7 +6704,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="49"/>
       <c r="H66" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -6719,7 +6716,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="49"/>
       <c r="H67" s="51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -6743,7 +6740,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="49"/>
       <c r="H69" s="26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -6755,7 +6752,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="49"/>
       <c r="H70" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6767,12 +6764,12 @@
       <c r="F71" s="23"/>
       <c r="G71" s="47"/>
       <c r="H71" s="52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B72" s="19"/>
       <c r="C72" s="61" t="s">
@@ -6788,7 +6785,7 @@
       <c r="A73" s="25"/>
       <c r="B73" s="1"/>
       <c r="C73" s="62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -6800,7 +6797,7 @@
       <c r="A74" s="25"/>
       <c r="B74" s="1"/>
       <c r="C74" s="59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -6812,7 +6809,7 @@
       <c r="A75" s="25"/>
       <c r="B75" s="1"/>
       <c r="C75" s="62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -6836,7 +6833,7 @@
       <c r="A77" s="21"/>
       <c r="B77" s="23"/>
       <c r="C77" s="60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D77" s="23"/>
       <c r="E77" s="23"/>
@@ -6846,7 +6843,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="40" t="s">
@@ -6864,19 +6861,19 @@
       <c r="A79" s="31"/>
       <c r="B79" s="1"/>
       <c r="C79" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="26"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B80" s="37"/>
       <c r="C80" s="37"/>
@@ -6885,7 +6882,7 @@
       </c>
       <c r="E80" s="19"/>
       <c r="F80" s="56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>15</v>
@@ -6899,17 +6896,17 @@
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
       <c r="D81" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="H81" s="26" t="s">
         <v>96</v>
-      </c>
-      <c r="H81" s="69" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -6949,7 +6946,7 @@
         <v>15</v>
       </c>
       <c r="H84" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -6963,7 +6960,7 @@
         <v>99</v>
       </c>
       <c r="H85" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -6974,7 +6971,7 @@
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H86" s="51"/>
     </row>
@@ -6986,7 +6983,7 @@
       <c r="E87" s="23"/>
       <c r="F87" s="23"/>
       <c r="G87" s="47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H87" s="52"/>
     </row>
@@ -7009,7 +7006,7 @@
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
@@ -7054,10 +7051,10 @@
         <v>15</v>
       </c>
       <c r="G92" s="48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H92" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -7072,10 +7069,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H93" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -7114,7 +7111,7 @@
       <c r="E96" s="19"/>
       <c r="F96" s="19"/>
       <c r="G96" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H96" s="20"/>
     </row>
@@ -7123,7 +7120,7 @@
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -7152,7 +7149,7 @@
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H99" s="26"/>
     </row>
@@ -7164,7 +7161,7 @@
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H100" s="26"/>
     </row>
@@ -7409,7 +7406,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7426,7 +7423,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7443,7 +7440,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7460,7 +7457,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -7477,7 +7474,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -7494,7 +7491,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -7511,7 +7508,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7528,7 +7525,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7545,7 +7542,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7562,7 +7559,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7579,7 +7576,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7596,7 +7593,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7613,7 +7610,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7782,7 +7779,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7973,13 +7970,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2DAF3E2-8384-4621-B8C6-B2A168FC61AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F85ADEAF-2002-4827-B3D6-D214DB58F7D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1C5A47-85D1-4798-8C90-807825EC8D38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5314DF2-91A6-4B2E-8BCF-79E8C322F210}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{670A9ECD-95E7-439F-8A86-DBB1C41334FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EC6BF42-E38B-4470-B256-2F00664E7FEE}"/>
 </file>
--- a/Plannings 2026 S25.xlsx
+++ b/Plannings 2026 S25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BE0CE18-006B-4DAE-B16C-37980937CBF9}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2071C545-2610-45FF-887D-E4D8B5F42F01}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="141">
   <si>
     <t>Planning des salariés du 15/06/2026 au 21/06/2026</t>
   </si>
@@ -249,9 +249,6 @@
     <t>JARGUEL Thomas</t>
   </si>
   <si>
-    <t>16:00/23:40</t>
-  </si>
-  <si>
     <t>KABUNDA NDEKE Marvyn</t>
   </si>
   <si>
@@ -445,6 +442,9 @@
   </si>
   <si>
     <t>08:45/17:00</t>
+  </si>
+  <si>
+    <t>17:45/23:40</t>
   </si>
 </sst>
 </file>
@@ -883,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -918,16 +918,7 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -945,9 +936,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -957,49 +945,22 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1098,6 +1059,48 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3369,23 +3372,243 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3413,23 +3636,331 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3457,39 +3988,963 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFB8EE0-C663-491E-B1EC-889044AEA4D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="17335500"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60F75D0E-0321-45D9-918C-85925110EB1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9086850" y="3114675"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADF4C610-C697-496B-BEAE-D7D762AC7EC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9086850" y="3495675"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE23A878-B6AD-4F3D-AB8D-ED9C384607DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="4200525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3503,37 +4958,125 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1A9D2E7-7DC0-4B4E-ACCA-561A228C9132}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{025FED30-2205-4407-AB81-28ACEE133B29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73316998-191B-4B07-9D98-D4A6528831D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4962525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3547,37 +5090,257 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC0A1C29-3A36-4904-B7C6-8DB77401D18C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{403D27DD-DBF1-4A72-A183-931CA4B92113}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{121B01B4-D40A-4AEC-8011-D5E69137891A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4962525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4146A5EE-DC4D-4A38-A6EF-92687138775C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3E0A750-0D95-451B-B30A-B7C92EF922A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{870C8E55-0C59-46E6-8591-7B8299EDE2FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20982214" y="18070286"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3591,21 +5354,21 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B52AE02C-AEB5-4E8D-B7A7-85B98A28F2BA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3621,7 +5384,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
+          <a:off x="20982214" y="16301357"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3635,65 +5398,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C9A67EA-336A-4412-8488-64ED08C34F9C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3709,1635 +5428,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFB8EE0-C663-491E-B1EC-889044AEA4D2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="17335500"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60F75D0E-0321-45D9-918C-85925110EB1E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9086850" y="3114675"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADF4C610-C697-496B-BEAE-D7D762AC7EC7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9086850" y="3495675"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE23A878-B6AD-4F3D-AB8D-ED9C384607DC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1A9D2E7-7DC0-4B4E-ACCA-561A228C9132}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{025FED30-2205-4407-AB81-28ACEE133B29}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73316998-191B-4B07-9D98-D4A6528831D3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4962525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC0A1C29-3A36-4904-B7C6-8DB77401D18C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{403D27DD-DBF1-4A72-A183-931CA4B92113}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{121B01B4-D40A-4AEC-8011-D5E69137891A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4962525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4146A5EE-DC4D-4A38-A6EF-92687138775C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3E0A750-0D95-451B-B30A-B7C92EF922A9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="4200525"/>
+          <a:off x="24479250" y="15920357"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5719,156 +5810,156 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="52.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="D3" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="G3" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>82</v>
+      <c r="H3" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="40" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="20"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="42" t="s">
+      <c r="A6" s="67"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="24"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23" t="s">
+      <c r="A8" s="67"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19" t="s">
+      <c r="C9" s="16"/>
+      <c r="D9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="45" t="s">
+      <c r="A10" s="66"/>
+      <c r="B10" s="32" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="1"/>
@@ -5880,196 +5971,196 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="26"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="46" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="26"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="23" t="s">
+      <c r="A12" s="67"/>
+      <c r="B12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="60" t="s">
+      <c r="C12" s="19"/>
+      <c r="D12" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
-      <c r="B14" s="23" t="s">
+      <c r="A14" s="67"/>
+      <c r="B14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="24"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="30"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="67" t="s">
+      <c r="C16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="67" t="s">
+      <c r="F16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="67"/>
-      <c r="H16" s="68"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="55"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
-      <c r="B17" s="64" t="s">
+      <c r="A17" s="66"/>
+      <c r="B17" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="64" t="s">
+      <c r="C17" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="51"/>
+      <c r="H17" s="56"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="66"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="64" t="s">
+      <c r="D18" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="E17" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="64"/>
-      <c r="H17" s="69"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65" t="s">
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="56"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="66"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="65" t="s">
+      <c r="D19" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="69"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="66" t="s">
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="56"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="66"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="56"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="67"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="D19" s="66" t="s">
+      <c r="D21" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="69"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="63" t="s">
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="58"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="63" t="s">
+      <c r="C22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="69"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="21"/>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="70" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="71"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="19" t="s">
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="48" t="s">
+      <c r="G22" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="50" t="s">
+      <c r="H22" s="37" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
+      <c r="A23" s="66"/>
       <c r="B23" s="1" t="s">
         <v>33</v>
       </c>
@@ -6081,15 +6172,15 @@
       <c r="F23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="49" t="s">
+      <c r="G23" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="54" t="s">
+      <c r="H23" s="41" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
+      <c r="A24" s="66"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -6098,71 +6189,71 @@
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="55" t="s">
+      <c r="H24" s="42" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="21"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23" t="s">
+      <c r="A25" s="67"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="71" t="s">
-        <v>139</v>
+      <c r="H25" s="58" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="40" t="s">
+      <c r="D26" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="40" t="s">
+      <c r="E26" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="20"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="57" t="s">
+      <c r="A27" s="66"/>
+      <c r="B27" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="41" t="s">
+      <c r="E27" s="28" t="s">
         <v>42</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="26"/>
+      <c r="H27" s="21"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="43" t="s">
+      <c r="A28" s="66"/>
+      <c r="B28" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="43" t="s">
+      <c r="D28" s="30" t="s">
         <v>38</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -6170,17 +6261,17 @@
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="26"/>
+      <c r="H28" s="21"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="41" t="s">
+      <c r="A29" s="66"/>
+      <c r="B29" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="41" t="s">
+      <c r="D29" s="28" t="s">
         <v>47</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -6188,12 +6279,12 @@
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="26"/>
+      <c r="H29" s="21"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="43" t="s">
+      <c r="A30" s="66"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="30" t="s">
         <v>38</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -6202,12 +6293,12 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="26"/>
+      <c r="H30" s="21"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="25"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41" t="s">
+      <c r="A31" s="66"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28" t="s">
         <v>50</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -6216,314 +6307,314 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="26"/>
+      <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="25"/>
-      <c r="B32" s="41"/>
+      <c r="A32" s="66"/>
+      <c r="B32" s="28"/>
       <c r="C32" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="43" t="s">
+      <c r="D32" s="30" t="s">
         <v>38</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="26"/>
+      <c r="H32" s="21"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="25"/>
-      <c r="B33" s="41"/>
+      <c r="A33" s="66"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D33" s="41" t="s">
+      <c r="D33" s="28" t="s">
         <v>53</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="26"/>
+      <c r="H33" s="21"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="25"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="43" t="s">
+      <c r="A34" s="66"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="41"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="26"/>
+      <c r="H34" s="21"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="31"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="41" t="s">
+      <c r="A35" s="69"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="41"/>
+      <c r="D35" s="28"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="26"/>
+      <c r="H35" s="21"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="40" t="s">
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="40" t="s">
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="20"/>
+      <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="21"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="42" t="s">
+      <c r="A37" s="67"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="24"/>
+      <c r="H37" s="20"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="40" t="s">
+      <c r="D38" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F38" s="40" t="s">
+      <c r="F38" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G38" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H38" s="20"/>
+      <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="25"/>
-      <c r="B39" s="41" t="s">
+      <c r="A39" s="66"/>
+      <c r="B39" s="28" t="s">
         <v>58</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="41" t="s">
+      <c r="D39" s="28" t="s">
         <v>59</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F39" s="41" t="s">
+      <c r="F39" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="G39" s="41" t="s">
+      <c r="G39" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="26"/>
+      <c r="H39" s="21"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="25"/>
-      <c r="B40" s="41"/>
+      <c r="A40" s="66"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="43" t="s">
+      <c r="F40" s="28"/>
+      <c r="G40" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H40" s="26"/>
+      <c r="H40" s="21"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="25"/>
-      <c r="B41" s="41"/>
+      <c r="A41" s="66"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E41" s="1"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41" t="s">
+      <c r="F41" s="28"/>
+      <c r="G41" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="H41" s="26"/>
+      <c r="H41" s="21"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
-      <c r="B42" s="41"/>
+      <c r="A42" s="66"/>
+      <c r="B42" s="28"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="43" t="s">
+      <c r="D42" s="30" t="s">
         <v>57</v>
       </c>
       <c r="E42" s="1"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="26"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="21"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="25"/>
-      <c r="B43" s="41"/>
+      <c r="A43" s="66"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="41" t="s">
+      <c r="D43" s="28" t="s">
         <v>63</v>
       </c>
       <c r="E43" s="1"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="26"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="21"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="25"/>
-      <c r="B44" s="41"/>
+      <c r="A44" s="66"/>
+      <c r="B44" s="28"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="59" t="s">
+      <c r="D44" s="46" t="s">
         <v>64</v>
       </c>
       <c r="E44" s="1"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="26"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="21"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="21"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="60" t="s">
+      <c r="A45" s="67"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="E45" s="23"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
-      <c r="H45" s="24"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="20"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19" t="s">
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="20"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="21"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23" t="s">
+      <c r="A47" s="67"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E47" s="23" t="s">
+      <c r="E47" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="24"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="20"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="H48" s="20"/>
+      <c r="A48" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="H48" s="17"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="25"/>
+      <c r="A49" s="66"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="41" t="s">
+      <c r="D49" s="28" t="s">
         <v>69</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-      <c r="G49" s="49" t="s">
+      <c r="G49" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="H49" s="26"/>
+      <c r="H49" s="21"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="25"/>
+      <c r="A50" s="66"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="43" t="s">
-        <v>123</v>
+      <c r="D50" s="30" t="s">
+        <v>122</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-      <c r="G50" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="H50" s="26"/>
+      <c r="G50" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="H50" s="21"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="25"/>
+      <c r="A51" s="66"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="41" t="s">
+      <c r="D51" s="28" t="s">
         <v>70</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-      <c r="G51" s="49" t="s">
+      <c r="G51" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H51" s="26"/>
+      <c r="H51" s="21"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="25"/>
+      <c r="A52" s="66"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="49"/>
-      <c r="H52" s="26"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="21"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="25"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
@@ -6531,696 +6622,694 @@
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="49"/>
-      <c r="H53" s="26"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="21"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="25"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="26"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="21"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23" t="s">
+      <c r="A55" s="67"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="24"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="20"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="32" t="s">
+      <c r="A56" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="B56" s="33"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="35"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="17" t="s">
+      <c r="B56" s="62"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="64"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="20" t="s">
-        <v>15</v>
-      </c>
+      <c r="B57" s="59"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="60"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
+      <c r="H57" s="61"/>
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="24" t="s">
+      <c r="A58" s="22" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="27" t="s">
+      <c r="B58" s="59"/>
+      <c r="C58" s="60"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="60"/>
+      <c r="F58" s="60"/>
+      <c r="G58" s="60"/>
+      <c r="H58" s="61"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="B59" s="28"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
-      <c r="F59" s="29"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="30"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
-        <v>77</v>
-      </c>
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="16"/>
+      <c r="H59" s="17"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="67"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
       <c r="E60" s="19"/>
-      <c r="F60" s="40" t="s">
-        <v>12</v>
+      <c r="F60" s="29" t="s">
+        <v>58</v>
       </c>
       <c r="G60" s="19"/>
       <c r="H60" s="20"/>
     </row>
-    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="21"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="G61" s="23"/>
-      <c r="H61" s="24"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="B61" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="17"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="67"/>
+      <c r="B62" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="B62" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D62" s="61" t="s">
-        <v>64</v>
+      <c r="C62" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="D62" s="47" t="s">
+        <v>79</v>
       </c>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
       <c r="G62" s="19"/>
       <c r="H62" s="20"/>
     </row>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="21"/>
-      <c r="B63" s="60" t="s">
-        <v>79</v>
-      </c>
-      <c r="C63" s="60" t="s">
-        <v>79</v>
-      </c>
-      <c r="D63" s="60" t="s">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="24"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="H63" s="17" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="H64" s="20" t="s">
-        <v>15</v>
+      <c r="A64" s="66"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="H64" s="21" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="25"/>
+      <c r="A65" s="66"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="H65" s="26" t="s">
-        <v>84</v>
+      <c r="G65" s="36"/>
+      <c r="H65" s="40" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="25"/>
+      <c r="A66" s="66"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="49"/>
-      <c r="H66" s="53" t="s">
-        <v>82</v>
+      <c r="G66" s="36"/>
+      <c r="H66" s="38" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="25"/>
+      <c r="A67" s="66"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="49"/>
-      <c r="H67" s="51" t="s">
-        <v>85</v>
+      <c r="G67" s="36"/>
+      <c r="H67" s="24" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="25"/>
+      <c r="A68" s="66"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="49"/>
-      <c r="H68" s="36" t="s">
-        <v>15</v>
+      <c r="G68" s="36"/>
+      <c r="H68" s="21" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="25"/>
+      <c r="A69" s="66"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="49"/>
-      <c r="H69" s="26" t="s">
+      <c r="G69" s="36"/>
+      <c r="H69" s="40" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="67"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="34"/>
+      <c r="H70" s="39" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="25"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="53" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="21"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="52" t="s">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="65" t="s">
         <v>87</v>
       </c>
+      <c r="B71" s="16"/>
+      <c r="C71" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="17"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="B72" s="19"/>
-      <c r="C72" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="20"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="21"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="25"/>
+      <c r="A73" s="66"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="62" t="s">
-        <v>89</v>
+      <c r="C73" s="46" t="s">
+        <v>64</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="26"/>
+      <c r="H73" s="21"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="25"/>
+      <c r="A74" s="66"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="59" t="s">
-        <v>64</v>
+      <c r="C74" s="49" t="s">
+        <v>65</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="26"/>
+      <c r="H74" s="21"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="25"/>
+      <c r="A75" s="66"/>
       <c r="B75" s="1"/>
-      <c r="C75" s="62" t="s">
-        <v>65</v>
+      <c r="C75" s="46" t="s">
+        <v>22</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
-      <c r="H75" s="26"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="25"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="26"/>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="21"/>
-      <c r="B77" s="23"/>
-      <c r="C77" s="60" t="s">
+      <c r="H75" s="21"/>
+    </row>
+    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="67"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="20"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="D77" s="23"/>
-      <c r="E77" s="23"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="24"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="17" t="s">
+      <c r="B77" s="16"/>
+      <c r="C77" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H77" s="17"/>
+    </row>
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="69"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G78" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H78" s="21"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="B78" s="19"/>
-      <c r="C78" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G78" s="19"/>
-      <c r="H78" s="20"/>
-    </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="31"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G79" s="1"/>
-      <c r="H79" s="26"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" s="16"/>
+      <c r="F79" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="19" t="s">
+      <c r="A80" s="66"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H80" s="56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="66"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E80" s="19"/>
-      <c r="F80" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="G80" s="19" t="s">
+      <c r="G81" s="1"/>
+      <c r="H81" s="21"/>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="67"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="19"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="G82" s="19"/>
+      <c r="H82" s="20"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="65" t="s">
+        <v>97</v>
+      </c>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H80" s="20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="25"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="15"/>
-      <c r="D81" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E81" s="1"/>
-      <c r="F81" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H81" s="69" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="25"/>
-      <c r="B82" s="15"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G82" s="1"/>
-      <c r="H82" s="26"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="21"/>
-      <c r="B83" s="38"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="23"/>
-      <c r="E83" s="23"/>
-      <c r="F83" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="G83" s="23"/>
-      <c r="H83" s="24"/>
+      <c r="H83" s="37" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="17" t="s">
+      <c r="A84" s="66"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="19"/>
-      <c r="G84" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" s="50" t="s">
+      <c r="H84" s="38" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="25"/>
+      <c r="A85" s="66"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="1" t="s">
+      <c r="G85" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H85" s="38"/>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="67"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="19"/>
+      <c r="E86" s="19"/>
+      <c r="F86" s="19"/>
+      <c r="G86" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H86" s="39"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="H85" s="51" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="25"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="46" t="s">
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="17"/>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="69"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="H86" s="51"/>
-    </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="21"/>
-      <c r="B87" s="23"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="23"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="23"/>
-      <c r="G87" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="H87" s="52"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="17" t="s">
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="21"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-      <c r="D88" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="E88" s="19"/>
-      <c r="F88" s="19"/>
-      <c r="G88" s="19"/>
-      <c r="H88" s="20"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="31"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="26"/>
+      <c r="B89" s="59"/>
+      <c r="C89" s="60"/>
+      <c r="D89" s="60"/>
+      <c r="E89" s="60"/>
+      <c r="F89" s="60"/>
+      <c r="G89" s="60"/>
+      <c r="H89" s="61"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="27" t="s">
+      <c r="A90" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="28"/>
-      <c r="C90" s="29"/>
-      <c r="D90" s="29"/>
-      <c r="E90" s="29"/>
-      <c r="F90" s="29"/>
-      <c r="G90" s="29"/>
-      <c r="H90" s="30"/>
-    </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="27" t="s">
+      <c r="B90" s="59"/>
+      <c r="C90" s="60"/>
+      <c r="D90" s="60"/>
+      <c r="E90" s="60"/>
+      <c r="F90" s="60"/>
+      <c r="G90" s="60"/>
+      <c r="H90" s="61"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="B91" s="28"/>
-      <c r="C91" s="29"/>
-      <c r="D91" s="29"/>
-      <c r="E91" s="29"/>
-      <c r="F91" s="29"/>
-      <c r="G91" s="29"/>
-      <c r="H91" s="30"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="16"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G91" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="H91" s="37" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G92" s="48" t="s">
+      <c r="A92" s="66"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="H92" s="50" t="s">
+      <c r="H92" s="38" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="25"/>
+      <c r="A93" s="66"/>
       <c r="B93" s="1"/>
-      <c r="C93" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="H93" s="51" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="25"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="2" t="s">
+      <c r="F93" s="1"/>
+      <c r="G93" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H94" s="51"/>
-    </row>
-    <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="21"/>
-      <c r="B95" s="23"/>
-      <c r="C95" s="23"/>
-      <c r="D95" s="23"/>
-      <c r="E95" s="23"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="23" t="s">
+      <c r="H93" s="24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="67"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="19"/>
+      <c r="D94" s="19"/>
+      <c r="E94" s="19"/>
+      <c r="F94" s="19"/>
+      <c r="G94" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H94" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="H95" s="52"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="16"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="H95" s="37" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="17" t="s">
+      <c r="A96" s="66"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="B96" s="19"/>
-      <c r="C96" s="19"/>
-      <c r="D96" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="E96" s="19"/>
-      <c r="F96" s="19"/>
-      <c r="G96" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="H96" s="20"/>
+      <c r="H96" s="38" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="25"/>
+      <c r="A97" s="66"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
-      <c r="D97" s="41" t="s">
-        <v>83</v>
-      </c>
+      <c r="D97" s="28"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
-      <c r="G97" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="H97" s="26"/>
+      <c r="G97" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" s="21"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="25"/>
+      <c r="A98" s="66"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
-      <c r="D98" s="41"/>
+      <c r="D98" s="28"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H98" s="26"/>
+      <c r="G98" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="H98" s="21"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="25"/>
+      <c r="A99" s="66"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
-      <c r="D99" s="41"/>
+      <c r="D99" s="28"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="H99" s="26"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="25"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="41"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="H100" s="26"/>
-    </row>
-    <row r="101" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="21"/>
-      <c r="B101" s="23"/>
-      <c r="C101" s="23"/>
-      <c r="D101" s="42"/>
-      <c r="E101" s="23"/>
-      <c r="F101" s="23"/>
-      <c r="G101" s="47" t="s">
-        <v>107</v>
-      </c>
-      <c r="H101" s="24"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B102" s="39"/>
-      <c r="C102" s="39"/>
-      <c r="D102" s="39"/>
-      <c r="E102" s="39"/>
-      <c r="F102" s="39"/>
-      <c r="G102" s="39"/>
-      <c r="H102" s="39"/>
+      <c r="G99" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H99" s="21"/>
+    </row>
+    <row r="100" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="67"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="19"/>
+      <c r="D100" s="29"/>
+      <c r="E100" s="19"/>
+      <c r="F100" s="19"/>
+      <c r="G100" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="H100" s="20"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B101" s="68"/>
+      <c r="C101" s="68"/>
+      <c r="D101" s="68"/>
+      <c r="E101" s="68"/>
+      <c r="F101" s="68"/>
+      <c r="G101" s="68"/>
+      <c r="H101" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B56:H56"/>
-    <mergeCell ref="B91:H91"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="A96:A101"/>
-    <mergeCell ref="B102:H102"/>
-    <mergeCell ref="A72:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A71"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A55"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B57:H57"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="A26:A35"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A70"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A55"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="A95:A100"/>
+    <mergeCell ref="B101:H101"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B89:H89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7239,36 +7328,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="71" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7511,7 +7600,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7528,7 +7617,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7545,7 +7634,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7562,7 +7651,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7579,7 +7668,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7596,7 +7685,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7613,7 +7702,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7630,7 +7719,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -7647,7 +7736,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -7664,7 +7753,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -7681,7 +7770,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -7698,7 +7787,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -7715,7 +7804,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -7765,40 +7854,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -7808,6 +7897,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F57AE488C1C9C348AE667C65EC1B6349" ma:contentTypeVersion="83" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="584bf6b77295f7da4f9cf4ac656056b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3c298670-db79-47a5-968d-a4570c34317f" xmlns:ns3="17e8e7ea-beb0-4155-adc4-5bfa61f32508" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0744868ac059cd1623b27209cff1bde4" ns2:_="" ns3:_="">
     <xsd:import namespace="3c298670-db79-47a5-968d-a4570c34317f"/>
@@ -7952,15 +8050,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7973,13 +8062,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2DAF3E2-8384-4621-B8C6-B2A168FC61AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1C5A47-85D1-4798-8C90-807825EC8D38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1C5A47-85D1-4798-8C90-807825EC8D38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2DAF3E2-8384-4621-B8C6-B2A168FC61AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{670A9ECD-95E7-439F-8A86-DBB1C41334FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{670A9ECD-95E7-439F-8A86-DBB1C41334FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Plannings 2026 S25.xlsx
+++ b/Plannings 2026 S25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2071C545-2610-45FF-887D-E4D8B5F42F01}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B195153-7FD2-4B51-B53A-E002631C3542}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="140">
   <si>
     <t>Planning des salariés du 15/06/2026 au 21/06/2026</t>
   </si>
@@ -316,9 +316,6 @@
   </si>
   <si>
     <t>RABII Mehdi</t>
-  </si>
-  <si>
-    <t>11:00/12:30</t>
   </si>
   <si>
     <t>SANGARNE Enzo</t>
@@ -883,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1101,6 +1098,12 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4208,23 +4211,199 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4252,23 +4431,199 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4296,23 +4651,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFB8EE0-C663-491E-B1EC-889044AEA4D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="17335500"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60F75D0E-0321-45D9-918C-85925110EB1E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4328,7 +4727,227 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
+          <a:off x="9086850" y="3114675"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADF4C610-C697-496B-BEAE-D7D762AC7EC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9086850" y="3495675"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE23A878-B6AD-4F3D-AB8D-ED9C384607DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1A9D2E7-7DC0-4B4E-ACCA-561A228C9132}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{025FED30-2205-4407-AB81-28ACEE133B29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73316998-191B-4B07-9D98-D4A6528831D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4962525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4342,65 +4961,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC0A1C29-3A36-4904-B7C6-8DB77401D18C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4416,7 +4991,139 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
+          <a:off x="1828800" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{403D27DD-DBF1-4A72-A183-931CA4B92113}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{121B01B4-D40A-4AEC-8011-D5E69137891A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4962525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4146A5EE-DC4D-4A38-A6EF-92687138775C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="4200525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4430,21 +5137,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3E0A750-0D95-451B-B30A-B7C92EF922A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4460,7 +5167,51 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
+          <a:off x="3048000" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{870C8E55-0C59-46E6-8591-7B8299EDE2FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20982214" y="18070286"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4474,21 +5225,21 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B52AE02C-AEB5-4E8D-B7A7-85B98A28F2BA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4504,51 +5255,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
+          <a:off x="20982214" y="16301357"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4562,849 +5269,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFB8EE0-C663-491E-B1EC-889044AEA4D2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="17335500"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60F75D0E-0321-45D9-918C-85925110EB1E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9086850" y="3114675"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADF4C610-C697-496B-BEAE-D7D762AC7EC7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9086850" y="3495675"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE23A878-B6AD-4F3D-AB8D-ED9C384607DC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1A9D2E7-7DC0-4B4E-ACCA-561A228C9132}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{025FED30-2205-4407-AB81-28ACEE133B29}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73316998-191B-4B07-9D98-D4A6528831D3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4962525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC0A1C29-3A36-4904-B7C6-8DB77401D18C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{403D27DD-DBF1-4A72-A183-931CA4B92113}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{121B01B4-D40A-4AEC-8011-D5E69137891A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4962525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4146A5EE-DC4D-4A38-A6EF-92687138775C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3E0A750-0D95-451B-B30A-B7C92EF922A9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{870C8E55-0C59-46E6-8591-7B8299EDE2FA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20982214" y="18070286"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B52AE02C-AEB5-4E8D-B7A7-85B98A28F2BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20982214" y="16301357"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5810,7 +5681,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="52.42578125" customWidth="1"/>
@@ -5840,22 +5711,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>137</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>81</v>
@@ -6067,10 +5938,10 @@
         <v>29</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E17" s="51" t="s">
         <v>30</v>
@@ -6085,10 +5956,10 @@
       <c r="A18" s="66"/>
       <c r="B18" s="51"/>
       <c r="C18" s="52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D18" s="52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
@@ -6099,10 +5970,10 @@
       <c r="A19" s="66"/>
       <c r="B19" s="51"/>
       <c r="C19" s="53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
@@ -6127,10 +5998,10 @@
       <c r="A21" s="67"/>
       <c r="B21" s="57"/>
       <c r="C21" s="57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D21" s="57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E21" s="57"/>
       <c r="F21" s="57"/>
@@ -6204,7 +6075,7 @@
         <v>35</v>
       </c>
       <c r="H25" s="58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6545,17 +6416,17 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="65" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E48" s="16"/>
       <c r="F48" s="16"/>
       <c r="G48" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H48" s="17"/>
     </row>
@@ -6578,12 +6449,12 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H50" s="21"/>
     </row>
@@ -6606,7 +6477,7 @@
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -6630,7 +6501,7 @@
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -6769,7 +6640,7 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H64" s="21" t="s">
         <v>83</v>
@@ -6990,7 +6861,7 @@
         <v>95</v>
       </c>
       <c r="H80" s="56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -7017,8 +6888,8 @@
       <c r="G82" s="19"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="65" t="s">
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="14" t="s">
         <v>97</v>
       </c>
       <c r="B83" s="16"/>
@@ -7034,252 +6905,214 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1" t="s">
+      <c r="A84" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="H84" s="38" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="66"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="16"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="17"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="69"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
+      <c r="D85" s="28" t="s">
+        <v>82</v>
+      </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="33" t="s">
+      <c r="G85" s="1"/>
+      <c r="H85" s="21"/>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B86" s="59"/>
+      <c r="C86" s="60"/>
+      <c r="D86" s="60"/>
+      <c r="E86" s="60"/>
+      <c r="F86" s="60"/>
+      <c r="G86" s="60"/>
+      <c r="H86" s="61"/>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" s="59"/>
+      <c r="C87" s="60"/>
+      <c r="D87" s="60"/>
+      <c r="E87" s="60"/>
+      <c r="F87" s="60"/>
+      <c r="G87" s="60"/>
+      <c r="H87" s="61"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="16"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="H85" s="38"/>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="67"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="19"/>
-      <c r="G86" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="H86" s="39"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="65" t="s">
-        <v>99</v>
-      </c>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="27" t="s">
+      <c r="H88" s="37" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="66"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="H89" s="38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="66"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="67"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="19"/>
+      <c r="E91" s="19"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H91" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="65" t="s">
+        <v>103</v>
+      </c>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E87" s="16"/>
-      <c r="F87" s="16"/>
-      <c r="G87" s="16"/>
-      <c r="H87" s="17"/>
-    </row>
-    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="69"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="21"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="B89" s="59"/>
-      <c r="C89" s="60"/>
-      <c r="D89" s="60"/>
-      <c r="E89" s="60"/>
-      <c r="F89" s="60"/>
-      <c r="G89" s="60"/>
-      <c r="H89" s="61"/>
-    </row>
-    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="B90" s="59"/>
-      <c r="C90" s="60"/>
-      <c r="D90" s="60"/>
-      <c r="E90" s="60"/>
-      <c r="F90" s="60"/>
-      <c r="G90" s="60"/>
-      <c r="H90" s="61"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G91" s="35" t="s">
+      <c r="E92" s="16"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="H92" s="37" t="s">
         <v>81</v>
-      </c>
-      <c r="H91" s="37" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="66"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="H92" s="38" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="66"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
+      <c r="D93" s="28" t="s">
+        <v>82</v>
+      </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
-      <c r="G93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H93" s="24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="67"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="19"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="19"/>
-      <c r="F94" s="19"/>
-      <c r="G94" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="H94" s="20" t="s">
-        <v>140</v>
-      </c>
+      <c r="G93" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="H93" s="38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="66"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="28"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="H94" s="73"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="B95" s="16"/>
-      <c r="C95" s="16"/>
-      <c r="D95" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E95" s="16"/>
-      <c r="F95" s="16"/>
-      <c r="G95" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="H95" s="37" t="s">
-        <v>81</v>
-      </c>
+      <c r="A95" s="66"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="28"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="H95" s="73"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="66"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
-      <c r="D96" s="28" t="s">
-        <v>82</v>
-      </c>
+      <c r="D96" s="28"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="28" t="s">
+      <c r="G96" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H96" s="73"/>
+    </row>
+    <row r="97" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="67"/>
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="29"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
+      <c r="G97" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="H96" s="38" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="66"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="28"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="H97" s="21"/>
+      <c r="H97" s="74"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="66"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="28"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="H98" s="21"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="66"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="28"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="H99" s="21"/>
-    </row>
-    <row r="100" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="67"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="29"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="19"/>
-      <c r="G100" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="H100" s="20"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B101" s="68"/>
-      <c r="C101" s="68"/>
-      <c r="D101" s="68"/>
-      <c r="E101" s="68"/>
-      <c r="F101" s="68"/>
-      <c r="G101" s="68"/>
-      <c r="H101" s="68"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="68"/>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="68"/>
+      <c r="H98" s="68"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
@@ -7297,19 +7130,18 @@
     <mergeCell ref="A38:A45"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A48:A55"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="A95:A100"/>
-    <mergeCell ref="B101:H101"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="A92:A97"/>
+    <mergeCell ref="B98:H98"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="A77:A78"/>
     <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="A84:A85"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B56:H56"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="B86:H86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7329,7 +7161,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
@@ -7337,7 +7169,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="72"/>
       <c r="D5" s="72"/>
@@ -7348,16 +7180,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7736,7 +7568,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -7753,7 +7585,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -7770,7 +7602,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -7787,7 +7619,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -7804,7 +7636,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -7854,21 +7686,21 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>91</v>
@@ -7876,18 +7708,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>117</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S25.xlsx
+++ b/Plannings 2026 S25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B195153-7FD2-4B51-B53A-E002631C3542}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{60C05D39-6B12-47A7-ACC9-538D34661BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2071C545-2610-45FF-887D-E4D8B5F42F01}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="141">
   <si>
     <t>Planning des salariés du 15/06/2026 au 21/06/2026</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>RABII Mehdi</t>
+  </si>
+  <si>
+    <t>11:00/12:30</t>
   </si>
   <si>
     <t>SANGARNE Enzo</t>
@@ -880,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1098,12 +1101,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4211,15 +4208,147 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4257,13 +4386,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4301,13 +4430,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4345,13 +4474,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4389,13 +4518,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4433,13 +4562,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4477,13 +4606,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4521,13 +4650,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4565,13 +4694,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4609,13 +4738,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5181,13 +5310,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5269,13 +5398,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5681,7 +5810,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="52.42578125" customWidth="1"/>
@@ -5711,22 +5840,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>81</v>
@@ -5938,10 +6067,10 @@
         <v>29</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E17" s="51" t="s">
         <v>30</v>
@@ -5956,10 +6085,10 @@
       <c r="A18" s="66"/>
       <c r="B18" s="51"/>
       <c r="C18" s="52" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D18" s="52" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
@@ -5970,10 +6099,10 @@
       <c r="A19" s="66"/>
       <c r="B19" s="51"/>
       <c r="C19" s="53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
@@ -5998,10 +6127,10 @@
       <c r="A21" s="67"/>
       <c r="B21" s="57"/>
       <c r="C21" s="57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D21" s="57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E21" s="57"/>
       <c r="F21" s="57"/>
@@ -6075,7 +6204,7 @@
         <v>35</v>
       </c>
       <c r="H25" s="58" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6416,17 +6545,17 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="65" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E48" s="16"/>
       <c r="F48" s="16"/>
       <c r="G48" s="35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H48" s="17"/>
     </row>
@@ -6449,12 +6578,12 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H50" s="21"/>
     </row>
@@ -6477,7 +6606,7 @@
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -6501,7 +6630,7 @@
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -6640,7 +6769,7 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H64" s="21" t="s">
         <v>83</v>
@@ -6861,7 +6990,7 @@
         <v>95</v>
       </c>
       <c r="H80" s="56" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -6888,8 +7017,8 @@
       <c r="G82" s="19"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="14" t="s">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="65" t="s">
         <v>97</v>
       </c>
       <c r="B83" s="16"/>
@@ -6905,214 +7034,252 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="65" t="s">
+      <c r="A84" s="66"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16"/>
-      <c r="H84" s="17"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="69"/>
+      <c r="H84" s="38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="66"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
-      <c r="D85" s="28" t="s">
-        <v>82</v>
-      </c>
+      <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="21"/>
+      <c r="G85" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H85" s="38"/>
     </row>
     <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="22" t="s">
+      <c r="A86" s="67"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="19"/>
+      <c r="E86" s="19"/>
+      <c r="F86" s="19"/>
+      <c r="G86" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H86" s="39"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="B86" s="59"/>
-      <c r="C86" s="60"/>
-      <c r="D86" s="60"/>
-      <c r="E86" s="60"/>
-      <c r="F86" s="60"/>
-      <c r="G86" s="60"/>
-      <c r="H86" s="61"/>
-    </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="22" t="s">
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="17"/>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="69"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="21"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B87" s="59"/>
-      <c r="C87" s="60"/>
-      <c r="D87" s="60"/>
-      <c r="E87" s="60"/>
-      <c r="F87" s="60"/>
-      <c r="G87" s="60"/>
-      <c r="H87" s="61"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="65" t="s">
+      <c r="B89" s="59"/>
+      <c r="C89" s="60"/>
+      <c r="D89" s="60"/>
+      <c r="E89" s="60"/>
+      <c r="F89" s="60"/>
+      <c r="G89" s="60"/>
+      <c r="H89" s="61"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B88" s="16"/>
-      <c r="C88" s="16" t="s">
+      <c r="B90" s="59"/>
+      <c r="C90" s="60"/>
+      <c r="D90" s="60"/>
+      <c r="E90" s="60"/>
+      <c r="F90" s="60"/>
+      <c r="G90" s="60"/>
+      <c r="H90" s="61"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
-      <c r="F88" s="16" t="s">
+      <c r="D91" s="16"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G88" s="35" t="s">
+      <c r="G91" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="H88" s="37" t="s">
+      <c r="H91" s="37" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="66"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1" t="s">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="66"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1" t="s">
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G89" s="36" t="s">
+      <c r="G92" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="H89" s="38" t="s">
+      <c r="H92" s="38" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="66"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" s="24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="67"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="19"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="19"/>
-      <c r="G91" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="H91" s="20" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="65" t="s">
-        <v>103</v>
-      </c>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="H92" s="37" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="66"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
-      <c r="D93" s="28" t="s">
-        <v>82</v>
-      </c>
+      <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
-      <c r="G93" s="28" t="s">
+      <c r="G93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" s="24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="67"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="19"/>
+      <c r="D94" s="19"/>
+      <c r="E94" s="19"/>
+      <c r="F94" s="19"/>
+      <c r="G94" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H94" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="H93" s="38" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="66"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="28"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="30" t="s">
+      <c r="B95" s="16"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H94" s="73"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="66"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="28"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="H95" s="73"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="H95" s="37" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="66"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
-      <c r="D96" s="28"/>
+      <c r="D96" s="28" t="s">
+        <v>82</v>
+      </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="33" t="s">
+      <c r="G96" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="H96" s="38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="66"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="28"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" s="21"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="66"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="28"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="H98" s="21"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="66"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="H96" s="73"/>
-    </row>
-    <row r="97" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="67"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="H97" s="74"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B98" s="68"/>
-      <c r="C98" s="68"/>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
-      <c r="H98" s="68"/>
+      <c r="H99" s="21"/>
+    </row>
+    <row r="100" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="67"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="19"/>
+      <c r="D100" s="29"/>
+      <c r="E100" s="19"/>
+      <c r="F100" s="19"/>
+      <c r="G100" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="H100" s="20"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B101" s="68"/>
+      <c r="C101" s="68"/>
+      <c r="D101" s="68"/>
+      <c r="E101" s="68"/>
+      <c r="F101" s="68"/>
+      <c r="G101" s="68"/>
+      <c r="H101" s="68"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
@@ -7130,18 +7297,19 @@
     <mergeCell ref="A38:A45"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A48:A55"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A92:A97"/>
-    <mergeCell ref="B98:H98"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="A95:A100"/>
+    <mergeCell ref="B101:H101"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="A77:A78"/>
     <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A87:A88"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B56:H56"/>
-    <mergeCell ref="B87:H87"/>
-    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B89:H89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7161,7 +7329,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="71" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
@@ -7169,7 +7337,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="72" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" s="72"/>
       <c r="D5" s="72"/>
@@ -7180,16 +7348,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7568,7 +7736,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -7585,7 +7753,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -7602,7 +7770,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -7619,7 +7787,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -7636,7 +7804,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -7686,21 +7854,21 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>91</v>
@@ -7708,18 +7876,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
